--- a/artfynd/A 44276-2025 artfynd.xlsx
+++ b/artfynd/A 44276-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133692556</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44276-2025 artfynd.xlsx
+++ b/artfynd/A 44276-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133692556</v>
       </c>
       <c r="B2" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44276-2025 artfynd.xlsx
+++ b/artfynd/A 44276-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133692556</v>
       </c>
       <c r="B2" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44276-2025 artfynd.xlsx
+++ b/artfynd/A 44276-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133692556</v>
       </c>
       <c r="B2" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44276-2025 artfynd.xlsx
+++ b/artfynd/A 44276-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133692556</v>
       </c>
       <c r="B2" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44276-2025 artfynd.xlsx
+++ b/artfynd/A 44276-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133692556</v>
+        <v>129297378</v>
       </c>
       <c r="B2" t="n">
-        <v>79366</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Småtjärnarna, Mpd</t>
+          <t>Skogen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589657</v>
+        <v>589708</v>
       </c>
       <c r="R2" t="n">
-        <v>6975520</v>
+        <v>6975716</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,43 +771,261 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129297379</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91905</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skogen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>589696</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6975749</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133692556</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>589657</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6975520</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Ella Hambeson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Ella Hambeson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44276-2025 artfynd.xlsx
+++ b/artfynd/A 44276-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297378</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129297379</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,8 +1041,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133692556</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>